--- a/catalogapp/catalogdata/SUPREME SALES.xlsx
+++ b/catalogapp/catalogdata/SUPREME SALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>SOLD LOTS</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Purchase Price</t>
   </si>
   <si>
-    <t>ExRate on Purchase Date</t>
+    <t>Link to Sale</t>
   </si>
   <si>
     <t>Purchase Price $</t>
@@ -136,7 +136,7 @@
     <t>£ Pounds</t>
   </si>
   <si>
-    <t>-</t>
+    <t>https://www.phillips.com/detail/david-hockney/220117?utm_source=chatgpt.com</t>
   </si>
   <si>
     <t>Oliver</t>
@@ -157,10 +157,16 @@
     <t>Celia Reclining</t>
   </si>
   <si>
+    <t>https://www.phillips.com/detail/%E5%A4%A7%E8%A1%9B%C2%B7%E9%9C%8D%E5%85%8B%E5%B0%BC/220118?utm_source=chatgpt.com</t>
+  </si>
+  <si>
     <t>Celia Looks</t>
   </si>
   <si>
     <t>FORUM</t>
+  </si>
+  <si>
+    <t>https://www.forumauctions.co.uk/150559/David-Hockney-b.1937-Celia-Looks-MCA-Tokyo-247-SAC-111?auction_date=&amp;auction_no=1167&amp;catId=&amp;excl_keyword=&amp;first_name=&amp;gridtype=listview&amp;high_estimate=&amp;ipp=10&amp;keyword=&amp;last_name=&amp;low_estimate=&amp;name=&amp;page_no=3&amp;search_type=&amp;sort_by=hammer_high_low&amp;tab_type=&amp;title=&amp;view=lot_detail</t>
   </si>
   <si>
     <t>Larsen</t>
@@ -175,10 +181,16 @@
     <t>Bonhams NY</t>
   </si>
   <si>
+    <t>https://www.bonhams.com/auction/30810/lot/33/joan-miro-1893-1983-grans-rupestres-vii/?utm_source=chatgpt.com</t>
+  </si>
+  <si>
     <t>Total Profits</t>
   </si>
   <si>
     <t>Total ROI</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>TOTAL TIME</t>
@@ -211,7 +223,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -292,6 +304,12 @@
     <font>
       <sz val="12.0"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -535,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -646,6 +664,9 @@
     <xf borderId="7" fillId="8" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="8" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="7" fillId="8" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -667,7 +688,7 @@
     <xf borderId="7" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="7" fillId="3" fontId="1" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -695,7 +716,7 @@
     <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="14" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -716,7 +737,7 @@
     </xf>
     <xf borderId="8" fillId="3" fontId="13" numFmtId="167" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="8" fillId="3" fontId="1" numFmtId="10" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="8" fillId="12" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="8" fillId="12" fontId="16" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -730,14 +751,14 @@
     <xf borderId="7" fillId="10" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -745,29 +766,29 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="171" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -1239,7 +1260,7 @@
       <c r="N5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
         <v>14</v>
       </c>
       <c r="P5" s="10" t="s">
@@ -1464,7 +1485,7 @@
       <c r="N9" s="45">
         <v>7500.0</v>
       </c>
-      <c r="O9" s="32" t="s">
+      <c r="O9" s="46" t="s">
         <v>41</v>
       </c>
       <c r="P9" s="45">
@@ -1475,43 +1496,43 @@
         <f t="shared" ref="Q9:Q12" si="5">P9 - R9 - S9</f>
         <v>7095</v>
       </c>
-      <c r="R9" s="46">
+      <c r="R9" s="47">
         <v>280.0</v>
       </c>
-      <c r="S9" s="46">
+      <c r="S9" s="47">
         <v>125.0</v>
       </c>
-      <c r="T9" s="47">
+      <c r="T9" s="48">
         <v>300.0</v>
       </c>
-      <c r="U9" s="48" t="s">
+      <c r="U9" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="49">
+      <c r="V9" s="50">
         <v>300.0</v>
       </c>
-      <c r="W9" s="49">
+      <c r="W9" s="50">
         <v>0.0</v>
       </c>
-      <c r="X9" s="49">
+      <c r="X9" s="50">
         <v>0.0</v>
       </c>
-      <c r="Y9" s="49">
+      <c r="Y9" s="50">
         <v>0.0</v>
       </c>
-      <c r="Z9" s="48" t="s">
+      <c r="Z9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="AA9" s="49">
+      <c r="AA9" s="50">
         <v>0.0</v>
       </c>
-      <c r="AB9" s="49">
+      <c r="AB9" s="50">
         <v>0.0</v>
       </c>
-      <c r="AC9" s="49">
+      <c r="AC9" s="50">
         <v>0.0</v>
       </c>
-      <c r="AD9" s="50">
+      <c r="AD9" s="51">
         <f t="shared" ref="AD9:AD12" si="6">M9-P9-T9</f>
         <v>1244</v>
       </c>
@@ -1524,7 +1545,7 @@
       <c r="AG9" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="AH9" s="51">
+      <c r="AH9" s="52">
         <f t="shared" ref="AH9:AH12" si="7">(AD9/(P9+T9))/(AI9/365)</f>
         <v>0.2064284415</v>
       </c>
@@ -1580,8 +1601,8 @@
       <c r="N10" s="45">
         <v>3750.0</v>
       </c>
-      <c r="O10" s="32" t="s">
-        <v>41</v>
+      <c r="O10" s="46" t="s">
+        <v>48</v>
       </c>
       <c r="P10" s="45">
         <f t="shared" si="4"/>
@@ -1591,43 +1612,43 @@
         <f t="shared" si="5"/>
         <v>3345</v>
       </c>
-      <c r="R10" s="46">
+      <c r="R10" s="47">
         <v>280.0</v>
       </c>
-      <c r="S10" s="46">
+      <c r="S10" s="47">
         <v>125.0</v>
       </c>
-      <c r="T10" s="47">
+      <c r="T10" s="48">
         <v>0.0</v>
       </c>
-      <c r="U10" s="48" t="s">
+      <c r="U10" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="V10" s="47">
+      <c r="V10" s="48">
         <v>0.0</v>
       </c>
-      <c r="W10" s="47">
+      <c r="W10" s="48">
         <v>0.0</v>
       </c>
-      <c r="X10" s="47">
+      <c r="X10" s="48">
         <v>0.0</v>
       </c>
-      <c r="Y10" s="47">
+      <c r="Y10" s="48">
         <v>0.0</v>
       </c>
-      <c r="Z10" s="48" t="s">
+      <c r="Z10" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="AA10" s="47">
+      <c r="AA10" s="48">
         <v>0.0</v>
       </c>
-      <c r="AB10" s="47">
+      <c r="AB10" s="48">
         <v>0.0</v>
       </c>
-      <c r="AC10" s="47">
+      <c r="AC10" s="48">
         <v>0.0</v>
       </c>
-      <c r="AD10" s="50">
+      <c r="AD10" s="51">
         <f t="shared" si="6"/>
         <v>126</v>
       </c>
@@ -1640,7 +1661,7 @@
       <c r="AG10" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="AH10" s="51">
+      <c r="AH10" s="52">
         <f t="shared" si="7"/>
         <v>0.0434893617</v>
       </c>
@@ -1664,10 +1685,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="41">
         <v>0.0</v>
@@ -1696,7 +1717,9 @@
       <c r="N11" s="45">
         <v>6875.0</v>
       </c>
-      <c r="O11" s="32"/>
+      <c r="O11" s="46" t="s">
+        <v>51</v>
+      </c>
       <c r="P11" s="45">
         <f t="shared" si="4"/>
         <v>6875</v>
@@ -1705,43 +1728,43 @@
         <f t="shared" si="5"/>
         <v>6470</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="47">
         <v>280.0</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="47">
         <v>125.0</v>
       </c>
-      <c r="T11" s="47">
+      <c r="T11" s="48">
         <v>0.0</v>
       </c>
-      <c r="U11" s="48" t="s">
+      <c r="U11" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="V11" s="47">
+      <c r="V11" s="48">
         <v>0.0</v>
       </c>
-      <c r="W11" s="47">
+      <c r="W11" s="48">
         <v>0.0</v>
       </c>
-      <c r="X11" s="47">
+      <c r="X11" s="48">
         <v>0.0</v>
       </c>
-      <c r="Y11" s="47">
+      <c r="Y11" s="48">
         <v>0.0</v>
       </c>
-      <c r="Z11" s="48" t="s">
+      <c r="Z11" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="AA11" s="47">
+      <c r="AA11" s="48">
         <v>0.0</v>
       </c>
-      <c r="AB11" s="47">
+      <c r="AB11" s="48">
         <v>0.0</v>
       </c>
-      <c r="AC11" s="47">
+      <c r="AC11" s="48">
         <v>0.0</v>
       </c>
-      <c r="AD11" s="50">
+      <c r="AD11" s="51">
         <f t="shared" si="6"/>
         <v>93</v>
       </c>
@@ -1749,12 +1772,12 @@
         <v>45584.0</v>
       </c>
       <c r="AF11" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AG11" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="AH11" s="51">
+      <c r="AH11" s="52">
         <f t="shared" si="7"/>
         <v>0.01877359143</v>
       </c>
@@ -1775,13 +1798,13 @@
         <v>45799.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" s="41">
         <v>0.05</v>
@@ -1810,7 +1833,9 @@
       <c r="N12" s="45">
         <v>5000.0</v>
       </c>
-      <c r="O12" s="32"/>
+      <c r="O12" s="46" t="s">
+        <v>56</v>
+      </c>
       <c r="P12" s="45">
         <f t="shared" si="4"/>
         <v>5000</v>
@@ -1819,43 +1844,43 @@
         <f t="shared" si="5"/>
         <v>4595</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="47">
         <v>280.0</v>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="47">
         <v>125.0</v>
       </c>
-      <c r="T12" s="47">
+      <c r="T12" s="48">
         <v>120.0</v>
       </c>
-      <c r="U12" s="48" t="s">
+      <c r="U12" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="V12" s="49">
+      <c r="V12" s="50">
         <v>120.0</v>
       </c>
-      <c r="W12" s="49">
+      <c r="W12" s="50">
         <v>0.0</v>
       </c>
-      <c r="X12" s="49">
+      <c r="X12" s="50">
         <v>0.0</v>
       </c>
-      <c r="Y12" s="49">
+      <c r="Y12" s="50">
         <v>0.0</v>
       </c>
-      <c r="Z12" s="48" t="s">
+      <c r="Z12" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="AA12" s="49">
+      <c r="AA12" s="50">
         <v>0.0</v>
       </c>
-      <c r="AB12" s="49">
+      <c r="AB12" s="50">
         <v>0.0</v>
       </c>
-      <c r="AC12" s="49">
+      <c r="AC12" s="50">
         <v>0.0</v>
       </c>
-      <c r="AD12" s="50">
+      <c r="AD12" s="51">
         <f t="shared" si="6"/>
         <v>580</v>
       </c>
@@ -1863,12 +1888,12 @@
         <v>45584.0</v>
       </c>
       <c r="AF12" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AG12" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="AH12" s="51">
+      <c r="AH12" s="52">
         <f t="shared" si="7"/>
         <v>0.1923146802</v>
       </c>
@@ -1885,7 +1910,7 @@
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="52"/>
+      <c r="E13" s="53"/>
       <c r="F13" s="24"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26"/>
@@ -1923,7 +1948,7 @@
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="24"/>
-      <c r="E14" s="52"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="24"/>
       <c r="G14" s="25"/>
       <c r="H14" s="26"/>
@@ -1958,79 +1983,79 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="63"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="60"/>
-      <c r="AD15" s="64"/>
-      <c r="AE15" s="54"/>
-      <c r="AF15" s="55"/>
-      <c r="AG15" s="55"/>
-      <c r="AH15" s="65"/>
-      <c r="AI15" s="55"/>
-      <c r="AJ15" s="66"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="63"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="61"/>
+      <c r="Z15" s="64"/>
+      <c r="AA15" s="61"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="61"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="55"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="66"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="67"/>
     </row>
     <row r="16" ht="6.75" customHeight="1">
       <c r="A16" s="8"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="69"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="70"/>
+      <c r="G16" s="71"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="75"/>
-      <c r="V16" s="72"/>
-      <c r="W16" s="72"/>
-      <c r="X16" s="72"/>
-      <c r="Y16" s="72"/>
-      <c r="Z16" s="75"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="72"/>
-      <c r="AC16" s="72"/>
-      <c r="AD16" s="76"/>
-      <c r="AE16" s="68"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="73"/>
+      <c r="U16" s="76"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="76"/>
+      <c r="AA16" s="73"/>
+      <c r="AB16" s="73"/>
+      <c r="AC16" s="73"/>
+      <c r="AD16" s="77"/>
+      <c r="AE16" s="69"/>
       <c r="AF16" s="8"/>
       <c r="AG16" s="8"/>
-      <c r="AH16" s="77"/>
+      <c r="AH16" s="78"/>
       <c r="AI16" s="8"/>
-      <c r="AJ16" s="74"/>
+      <c r="AJ16" s="75"/>
     </row>
     <row r="17" ht="24.0" customHeight="1">
       <c r="A17" s="6"/>
@@ -2062,14 +2087,14 @@
       <c r="AA17" s="6"/>
       <c r="AB17" s="6"/>
       <c r="AC17" s="6"/>
-      <c r="AD17" s="78" t="s">
-        <v>54</v>
+      <c r="AD17" s="79" t="s">
+        <v>57</v>
       </c>
       <c r="AE17" s="6"/>
       <c r="AF17" s="6"/>
       <c r="AG17" s="6"/>
-      <c r="AH17" s="78" t="s">
-        <v>55</v>
+      <c r="AH17" s="79" t="s">
+        <v>58</v>
       </c>
       <c r="AI17" s="6"/>
       <c r="AJ17" s="6"/>
@@ -2084,72 +2109,72 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="80">
+      <c r="J18" s="80"/>
+      <c r="K18" s="81">
         <f t="shared" ref="K18:M18" si="9">SUM(K8:K15)</f>
         <v>26568</v>
       </c>
-      <c r="L18" s="80">
+      <c r="L18" s="81">
         <f t="shared" si="9"/>
         <v>980</v>
       </c>
-      <c r="M18" s="80">
+      <c r="M18" s="81">
         <f t="shared" si="9"/>
         <v>25588</v>
       </c>
-      <c r="N18" s="81" t="s">
-        <v>41</v>
+      <c r="N18" s="82" t="s">
+        <v>59</v>
       </c>
-      <c r="O18" s="81" t="s">
-        <v>41</v>
+      <c r="O18" s="82" t="s">
+        <v>59</v>
       </c>
-      <c r="P18" s="82">
+      <c r="P18" s="83">
         <f t="shared" ref="P18:T18" si="10">SUM(P8:P15)</f>
         <v>23125</v>
       </c>
-      <c r="Q18" s="82">
+      <c r="Q18" s="83">
         <f t="shared" si="10"/>
         <v>21505</v>
       </c>
-      <c r="R18" s="82">
+      <c r="R18" s="83">
         <f t="shared" si="10"/>
         <v>1120</v>
       </c>
-      <c r="S18" s="82">
+      <c r="S18" s="83">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="T18" s="82">
+      <c r="T18" s="83">
         <f t="shared" si="10"/>
         <v>420</v>
       </c>
-      <c r="U18" s="83"/>
-      <c r="V18" s="82">
+      <c r="U18" s="84"/>
+      <c r="V18" s="83">
         <f t="shared" ref="V18:Y18" si="11">SUM(V8:V15)</f>
         <v>420</v>
       </c>
-      <c r="W18" s="82">
+      <c r="W18" s="83">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X18" s="82">
+      <c r="X18" s="83">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y18" s="82">
+      <c r="Y18" s="83">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="83"/>
-      <c r="AA18" s="82">
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="83">
         <f t="shared" ref="AA18:AC18" si="12">SUM(AA8:AA15)</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="82">
+      <c r="AB18" s="83">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC18" s="82">
+      <c r="AC18" s="83">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -2159,28 +2184,28 @@
       </c>
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
-      <c r="AG18" s="84" t="s">
-        <v>56</v>
+      <c r="AG18" s="85" t="s">
+        <v>60</v>
       </c>
       <c r="AH18" s="37">
         <f>(AD18/(P18+T18))/(AI18/365)</f>
         <v>0.1123087072</v>
       </c>
-      <c r="AI18" s="85">
+      <c r="AI18" s="86">
         <f>MAX(AI6:AI14)</f>
         <v>282</v>
       </c>
-      <c r="AJ18" s="85" t="s">
-        <v>57</v>
+      <c r="AJ18" s="86" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="21.0" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="88"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="89"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -2194,42 +2219,42 @@
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
-      <c r="T19" s="89"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="89"/>
-      <c r="W19" s="89"/>
-      <c r="X19" s="89"/>
-      <c r="Y19" s="89"/>
-      <c r="Z19" s="90"/>
-      <c r="AA19" s="89"/>
-      <c r="AB19" s="89"/>
-      <c r="AC19" s="89"/>
-      <c r="AD19" s="78" t="s">
-        <v>58</v>
+      <c r="T19" s="90"/>
+      <c r="U19" s="91"/>
+      <c r="V19" s="90"/>
+      <c r="W19" s="90"/>
+      <c r="X19" s="90"/>
+      <c r="Y19" s="90"/>
+      <c r="Z19" s="91"/>
+      <c r="AA19" s="90"/>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="79" t="s">
+        <v>62</v>
       </c>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
-      <c r="AG19" s="84" t="s">
-        <v>59</v>
+      <c r="AG19" s="85" t="s">
+        <v>63</v>
       </c>
       <c r="AH19" s="37">
         <f>(AD18/(P18+T18))/(AI19/365)</f>
         <v>0.1215779479</v>
       </c>
-      <c r="AI19" s="85">
+      <c r="AI19" s="86">
         <f>AVERAGE(AI6:AI14)</f>
         <v>260.5</v>
       </c>
-      <c r="AJ19" s="85" t="s">
-        <v>57</v>
+      <c r="AJ19" s="86" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -2244,24 +2269,24 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="89"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="89"/>
-      <c r="W20" s="89"/>
-      <c r="X20" s="89"/>
-      <c r="Y20" s="89"/>
-      <c r="Z20" s="90"/>
-      <c r="AA20" s="89"/>
-      <c r="AB20" s="89"/>
-      <c r="AC20" s="89"/>
+      <c r="T20" s="90"/>
+      <c r="U20" s="91"/>
+      <c r="V20" s="90"/>
+      <c r="W20" s="90"/>
+      <c r="X20" s="90"/>
+      <c r="Y20" s="90"/>
+      <c r="Z20" s="91"/>
+      <c r="AA20" s="90"/>
+      <c r="AB20" s="90"/>
+      <c r="AC20" s="90"/>
       <c r="AD20" s="34" t="str">
         <f>AF21</f>
         <v/>
       </c>
       <c r="AE20" s="6"/>
       <c r="AF20" s="6"/>
-      <c r="AG20" s="92"/>
-      <c r="AH20" s="93"/>
+      <c r="AG20" s="93"/>
+      <c r="AH20" s="94"/>
       <c r="AI20" s="6"/>
       <c r="AJ20" s="6"/>
     </row>
@@ -2295,12 +2320,12 @@
       <c r="AA21" s="6"/>
       <c r="AB21" s="6"/>
       <c r="AC21" s="6"/>
-      <c r="AD21" s="78" t="s">
-        <v>60</v>
+      <c r="AD21" s="79" t="s">
+        <v>64</v>
       </c>
       <c r="AE21" s="6"/>
-      <c r="AF21" s="94"/>
-      <c r="AG21" s="89"/>
+      <c r="AF21" s="95"/>
+      <c r="AG21" s="90"/>
       <c r="AH21" s="6"/>
       <c r="AI21" s="6"/>
       <c r="AJ21" s="6"/>
@@ -2308,7 +2333,7 @@
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="95"/>
+      <c r="C22" s="96"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -2346,7 +2371,7 @@
     <row r="23" ht="4.5" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
-      <c r="C23" s="95"/>
+      <c r="C23" s="96"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -2373,7 +2398,7 @@
       <c r="AA23" s="6"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
-      <c r="AD23" s="89"/>
+      <c r="AD23" s="90"/>
       <c r="AE23" s="6"/>
       <c r="AF23" s="6"/>
       <c r="AG23" s="6"/>
@@ -2384,7 +2409,7 @@
     <row r="24" ht="4.5" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
-      <c r="C24" s="95"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -2411,7 +2436,7 @@
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="89"/>
+      <c r="AD24" s="90"/>
       <c r="AE24" s="6"/>
       <c r="AF24" s="6"/>
       <c r="AG24" s="6"/>
@@ -2449,7 +2474,7 @@
       <c r="AA25" s="6"/>
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="89"/>
+      <c r="AD25" s="90"/>
       <c r="AE25" s="6"/>
       <c r="AF25" s="6"/>
       <c r="AG25" s="6"/>
@@ -2487,7 +2512,7 @@
       <c r="AA26" s="6"/>
       <c r="AB26" s="6"/>
       <c r="AC26" s="6"/>
-      <c r="AD26" s="89"/>
+      <c r="AD26" s="90"/>
       <c r="AE26" s="6"/>
       <c r="AF26" s="6"/>
       <c r="AG26" s="6"/>
@@ -2498,7 +2523,7 @@
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="96"/>
+      <c r="C27" s="97"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -2525,7 +2550,7 @@
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
       <c r="AC27" s="6"/>
-      <c r="AD27" s="89"/>
+      <c r="AD27" s="90"/>
       <c r="AE27" s="6"/>
       <c r="AF27" s="6"/>
       <c r="AG27" s="6"/>
@@ -2563,7 +2588,7 @@
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="89"/>
+      <c r="AD28" s="90"/>
       <c r="AE28" s="6"/>
       <c r="AF28" s="6"/>
       <c r="AG28" s="6"/>
@@ -2574,76 +2599,76 @@
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="97"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="97"/>
-      <c r="T29" s="97"/>
-      <c r="U29" s="97"/>
-      <c r="V29" s="97"/>
-      <c r="W29" s="97"/>
-      <c r="X29" s="97"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="97"/>
-      <c r="AA29" s="97"/>
-      <c r="AB29" s="97"/>
-      <c r="AC29" s="97"/>
-      <c r="AD29" s="97"/>
-      <c r="AE29" s="97"/>
-      <c r="AF29" s="97"/>
-      <c r="AG29" s="97"/>
-      <c r="AH29" s="97"/>
-      <c r="AI29" s="97"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="98"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="98"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="98"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="98"/>
+      <c r="AB29" s="98"/>
+      <c r="AC29" s="98"/>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="98"/>
+      <c r="AF29" s="98"/>
+      <c r="AG29" s="98"/>
+      <c r="AH29" s="98"/>
+      <c r="AI29" s="98"/>
       <c r="AJ29" s="6"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="100"/>
       <c r="F30" s="6"/>
-      <c r="G30" s="100"/>
+      <c r="G30" s="101"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="101"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="89"/>
-      <c r="R30" s="89"/>
-      <c r="S30" s="89"/>
-      <c r="T30" s="89"/>
-      <c r="U30" s="90"/>
-      <c r="V30" s="89"/>
-      <c r="W30" s="89"/>
-      <c r="X30" s="89"/>
-      <c r="Y30" s="89"/>
-      <c r="Z30" s="90"/>
-      <c r="AA30" s="89"/>
-      <c r="AB30" s="89"/>
-      <c r="AC30" s="89"/>
-      <c r="AD30" s="103"/>
-      <c r="AE30" s="98"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="91"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="90"/>
+      <c r="Z30" s="91"/>
+      <c r="AA30" s="90"/>
+      <c r="AB30" s="90"/>
+      <c r="AC30" s="90"/>
+      <c r="AD30" s="104"/>
+      <c r="AE30" s="99"/>
       <c r="AF30" s="6"/>
       <c r="AG30" s="6"/>
-      <c r="AH30" s="93"/>
+      <c r="AH30" s="94"/>
       <c r="AI30" s="6"/>
       <c r="AJ30" s="6"/>
     </row>
@@ -2705,17 +2730,17 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
-      <c r="T32" s="94"/>
+      <c r="T32" s="95"/>
       <c r="U32" s="7"/>
-      <c r="V32" s="94"/>
-      <c r="W32" s="94"/>
-      <c r="X32" s="94"/>
-      <c r="Y32" s="94"/>
+      <c r="V32" s="95"/>
+      <c r="W32" s="95"/>
+      <c r="X32" s="95"/>
+      <c r="Y32" s="95"/>
       <c r="Z32" s="7"/>
-      <c r="AA32" s="94"/>
-      <c r="AB32" s="94"/>
-      <c r="AC32" s="94"/>
-      <c r="AD32" s="104"/>
+      <c r="AA32" s="95"/>
+      <c r="AB32" s="95"/>
+      <c r="AC32" s="95"/>
+      <c r="AD32" s="105"/>
       <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
       <c r="AG32" s="6"/>
@@ -2905,11 +2930,11 @@
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
       <c r="AC37" s="6"/>
-      <c r="AD37" s="105"/>
+      <c r="AD37" s="106"/>
       <c r="AE37" s="6"/>
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
-      <c r="AH37" s="105"/>
+      <c r="AH37" s="106"/>
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
     </row>
@@ -2924,30 +2949,30 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="101"/>
-      <c r="L38" s="101"/>
-      <c r="M38" s="101"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="101"/>
-      <c r="Q38" s="101"/>
-      <c r="R38" s="101"/>
-      <c r="S38" s="101"/>
-      <c r="T38" s="89"/>
-      <c r="U38" s="90"/>
-      <c r="V38" s="89"/>
-      <c r="W38" s="89"/>
-      <c r="X38" s="89"/>
-      <c r="Y38" s="89"/>
-      <c r="Z38" s="90"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="89"/>
-      <c r="AC38" s="89"/>
-      <c r="AD38" s="106"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
+      <c r="S38" s="102"/>
+      <c r="T38" s="90"/>
+      <c r="U38" s="91"/>
+      <c r="V38" s="90"/>
+      <c r="W38" s="90"/>
+      <c r="X38" s="90"/>
+      <c r="Y38" s="90"/>
+      <c r="Z38" s="91"/>
+      <c r="AA38" s="90"/>
+      <c r="AB38" s="90"/>
+      <c r="AC38" s="90"/>
+      <c r="AD38" s="107"/>
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
       <c r="AG38" s="6"/>
-      <c r="AH38" s="93"/>
+      <c r="AH38" s="94"/>
       <c r="AI38" s="6"/>
       <c r="AJ38" s="6"/>
     </row>
@@ -2971,21 +2996,21 @@
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
-      <c r="T39" s="89"/>
-      <c r="U39" s="90"/>
-      <c r="V39" s="89"/>
-      <c r="W39" s="89"/>
-      <c r="X39" s="89"/>
-      <c r="Y39" s="89"/>
-      <c r="Z39" s="90"/>
-      <c r="AA39" s="89"/>
-      <c r="AB39" s="89"/>
-      <c r="AC39" s="89"/>
-      <c r="AD39" s="89"/>
+      <c r="T39" s="90"/>
+      <c r="U39" s="91"/>
+      <c r="V39" s="90"/>
+      <c r="W39" s="90"/>
+      <c r="X39" s="90"/>
+      <c r="Y39" s="90"/>
+      <c r="Z39" s="91"/>
+      <c r="AA39" s="90"/>
+      <c r="AB39" s="90"/>
+      <c r="AC39" s="90"/>
+      <c r="AD39" s="90"/>
       <c r="AE39" s="6"/>
       <c r="AF39" s="6"/>
       <c r="AG39" s="6"/>
-      <c r="AH39" s="93"/>
+      <c r="AH39" s="94"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
     </row>
@@ -3057,11 +3082,11 @@
       <c r="AA41" s="6"/>
       <c r="AB41" s="6"/>
       <c r="AC41" s="6"/>
-      <c r="AD41" s="105"/>
+      <c r="AD41" s="106"/>
       <c r="AE41" s="6"/>
       <c r="AF41" s="6"/>
       <c r="AG41" s="6"/>
-      <c r="AH41" s="105"/>
+      <c r="AH41" s="106"/>
       <c r="AI41" s="6"/>
       <c r="AJ41" s="6"/>
     </row>
@@ -3095,11 +3120,11 @@
       <c r="AA42" s="6"/>
       <c r="AB42" s="6"/>
       <c r="AC42" s="6"/>
-      <c r="AD42" s="89"/>
+      <c r="AD42" s="90"/>
       <c r="AE42" s="6"/>
       <c r="AF42" s="6"/>
-      <c r="AG42" s="92"/>
-      <c r="AH42" s="93"/>
+      <c r="AG42" s="93"/>
+      <c r="AH42" s="94"/>
       <c r="AI42" s="6"/>
       <c r="AJ42" s="6"/>
     </row>
@@ -3136,7 +3161,7 @@
       <c r="AD43" s="6"/>
       <c r="AE43" s="6"/>
       <c r="AF43" s="6"/>
-      <c r="AG43" s="92"/>
+      <c r="AG43" s="93"/>
       <c r="AH43" s="6"/>
       <c r="AI43" s="6"/>
       <c r="AJ43" s="6"/>
@@ -39518,9 +39543,15 @@
       <formula1>"Alex,Oliver,Jeremy,Split,Gift,TBD,N/A"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="O9"/>
+    <hyperlink r:id="rId2" ref="O10"/>
+    <hyperlink r:id="rId3" ref="O11"/>
+    <hyperlink r:id="rId4" ref="O12"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>